--- a/results/job_matches_2026-06-03.xlsx
+++ b/results/job_matches_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G162"/>
+  <dimension ref="A1:G152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - API Platform Engineer - CDH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KLS Martin Group</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, GCP</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Hive, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b464e799ea8089d</t>
+          <t>https://www.indeed.com/viewjob?jk=d846903d81c33e82</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - API Platform Engineer - CDH</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>IKS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hive, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d846903d81c33e82</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6b03669fcb256f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III: Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Bennett Family of Companies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McDonough, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6033e89c4de2fb1</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce5cf18206c40a5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI Platform Architect (contract)</t>
+          <t>Software Engineer III: Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4035741c18917073</t>
+          <t>https://www.indeed.com/viewjob?jk=a6033e89c4de2fb1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer (Remote US)</t>
+          <t>Cloud &amp; AI Platform Architect (contract)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b23c465617e6263</t>
+          <t>https://www.indeed.com/viewjob?jk=4035741c18917073</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Senior Engineer, AI Data Management</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Emmes Company, LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Scala, PostgreSQL</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ab205482e4b0a3</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae6b623863032dc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Scientist - Airvoyant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capstone Logistics, LLC</t>
+          <t>TRAX USA Corp.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7e3e5bab34cec5</t>
+          <t>https://www.indeed.com/viewjob?jk=f54bacadbab2a4ac</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Cloud Engineer (Remote US)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20490252a7282e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=3b23c465617e6263</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Analyst IV</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>The Emmes Company, LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Redmond, OR, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5018082608c39c</t>
+          <t>https://www.indeed.com/viewjob?jk=34ab205482e4b0a3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NLM Bioinformatics Specialist and Developer (SME) I - III</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PostgreSQL, MySQL, MongoDB, ETL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=762cbbd89d012daa</t>
+          <t>https://www.indeed.com/viewjob?jk=20490252a7282e6d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Engineer I, DevOps</t>
+          <t>Data &amp; Analytics Analyst IV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CareMetx, LLC</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redmond, OR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f343c9a6ac4261</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5018082608c39c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Senior Engineer I, DevOps</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>CareMetx, LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37cd157df749b9e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f343c9a6ac4261</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack and AI Engineer</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f94b5acff92730</t>
+          <t>https://www.indeed.com/viewjob?jk=37cd157df749b9e8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Full Stack and AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Varonis Systems</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Event Hubs, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,19 +951,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05047e3838d26d9</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f94b5acff92730</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Varonis Systems</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -972,11 +972,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Azure, Event Hubs, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32f15966adb7c80c</t>
+          <t>https://www.indeed.com/viewjob?jk=d05047e3838d26d9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer - API Platform Engineer - CDH</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Lasting Change Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edb333da77c178b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3a86d1b4b4bd7e7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc2c674a4afffb4</t>
+          <t>https://www.indeed.com/viewjob?jk=32f15966adb7c80c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - API Platform Engineer - CDH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbda51fe27c52909</t>
+          <t>https://www.indeed.com/viewjob?jk=edb333da77c178b4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Cloud Platform Engineer HYBRID - Cedar Park, TX (Austin area)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>James Avery</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a782b5d0ec36a3</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc2c674a4afffb4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e4e883bfa671e3</t>
+          <t>https://www.indeed.com/viewjob?jk=dbda51fe27c52909</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr Cloud Platform Engineer HYBRID - Cedar Park, TX (Austin area)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>James Avery</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6b0d07da6ac2093</t>
+          <t>https://www.indeed.com/viewjob?jk=21a782b5d0ec36a3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Healthcare Data Platforms</t>
+          <t>Sr. Technical Solutions Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Softchoice</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, GCP, BigQuery, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c87aef812edc38ba</t>
+          <t>https://www.indeed.com/viewjob?jk=2514cb3d6eaca2b7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324835225383dd25</t>
+          <t>https://www.indeed.com/viewjob?jk=e6b0d07da6ac2093</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Direct Travel</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashua, NH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b2c7b0108f721a</t>
+          <t>https://www.indeed.com/viewjob?jk=70728c10caf53950</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer – Healthcare Data Platforms</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c4f516403858ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=c87aef812edc38ba</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Konexus, Inc.</t>
+          <t>Direct Travel</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eagle, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01891cd9bc4d364f</t>
+          <t>https://www.indeed.com/viewjob?jk=32b2c7b0108f721a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fervo Energy</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, GCP, Spark, Snowflake</t>
+          <t>RDS, Azure, Data Factory, GCP, BigQuery, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e937b8d6d40093ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7c4f516403858ed9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Developer - Airvoyant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>TRAX USA Corp.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>S3, Azure, Cloud Storage, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b51410dd8ffd88</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1046b4cc869c21</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>S3, Azure, Cloud Storage, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fed518d6fe919b</t>
+          <t>https://www.indeed.com/viewjob?jk=c980ae96d7c71b5b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>S3, Azure, Cloud Storage, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cac809c2033ba77</t>
+          <t>https://www.indeed.com/viewjob?jk=25b51410dd8ffd88</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IT Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>S3, Azure, Cloud Storage, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac62be27b216f151</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fed518d6fe919b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Informatics Architect</t>
+          <t>IT Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Steerbridge</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Dimensional Modeling, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c1e23f8adfafe11</t>
+          <t>https://www.indeed.com/viewjob?jk=ac62be27b216f151</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Analyst, Customer Insights BI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>KeHE Distributors</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, Tableau, Python, SQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d48b73708859bddb</t>
+          <t>https://www.indeed.com/viewjob?jk=837c797913f92786</t>
         </is>
       </c>
     </row>
@@ -2078,25 +2078,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Analytics Software Engineer IV</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Synapse Health</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Skokie, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, EMR, Redshift, RDS, Spark, PySpark, Scala, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,19 +2106,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd0c42686d3c4d3</t>
+          <t>https://www.indeed.com/viewjob?jk=93d71aec8bc25826</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior QA Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Synapse Health</t>
+          <t>Ceresti Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2127,46 +2127,46 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Spark, PostgreSQL, Data Modeling, Kimball, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0053e93e2ff70b27</t>
+          <t>https://www.indeed.com/viewjob?jk=94bd4f4546ea6e61</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Informatica ETL Developer - 6326296</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837c797913f92786</t>
+          <t>https://www.indeed.com/viewjob?jk=40516db2dcf106b5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DATA ANALYST L3(CONTRACT)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Fashion Nova</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Beverly Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Jenkins, Jenkins, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65dda35913c82cc</t>
+          <t>https://www.indeed.com/viewjob?jk=b80f5d754f1ffd13</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Analytics Software Engineer IV</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Spark, PySpark, Scala, Tableau, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d71aec8bc25826</t>
+          <t>https://www.indeed.com/viewjob?jk=de8841e4e75fbe68</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ceresti Health</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PostgreSQL, Data Modeling, Kimball, dbt, CI/CD, Airflow</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94bd4f4546ea6e61</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ca03311ac42217</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fashion Nova</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, dbt, CI/CD, Airflow</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80f5d754f1ffd13</t>
+          <t>https://www.indeed.com/viewjob?jk=b9faea0d55a841c9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, CI/CD, Terraform, Airflow</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8841e4e75fbe68</t>
+          <t>https://www.indeed.com/viewjob?jk=2abbc5f73ae2028d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ca03311ac42217</t>
+          <t>https://www.indeed.com/viewjob?jk=33de66454718a7f8</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9faea0d55a841c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f96d64f561456df6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>General Intuition &amp; Medal</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abbc5f73ae2028d</t>
+          <t>https://www.indeed.com/viewjob?jk=235e8563d0407abd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability / Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Medal</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33de66454718a7f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd6b80058693cb4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Exostar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96d64f561456df6</t>
+          <t>https://www.indeed.com/viewjob?jk=9043dd14b9a4d11b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235e8563d0407abd</t>
+          <t>https://www.indeed.com/viewjob?jk=69b02ec8d04b37bb</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd6b80058693cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=3c25c1b0bc5a8d73</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Exostar</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9043dd14b9a4d11b</t>
+          <t>https://www.indeed.com/viewjob?jk=213170f837efaaa7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Senior Cloud Technical Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Cloud Storage, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c25c1b0bc5a8d73</t>
+          <t>https://www.indeed.com/viewjob?jk=fb363572dc01c51e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Cloud Technical Architect</t>
+          <t>Sr AI Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Cloud Storage, Scala, DynamoDB, NoSQL</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Snowflake, Time Travel, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb363572dc01c51e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e01343345f387b3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Cloud Technical Architect</t>
+          <t>Senior Data Modeler</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Davidson, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Cloud Storage, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc613361b67cb34</t>
+          <t>https://www.indeed.com/viewjob?jk=745e80023e3ea1c3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr AI Platform Engineer</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Snowflake, Time Travel, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e01343345f387b3</t>
+          <t>https://www.indeed.com/viewjob?jk=4a585d9e5f8d2b5e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Modeler</t>
+          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Davidson, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745e80023e3ea1c3</t>
+          <t>https://www.indeed.com/viewjob?jk=03e209bbb5ba8b89</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a585d9e5f8d2b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=a1aed5a774867a44</t>
         </is>
       </c>
     </row>
@@ -4353,25 +4353,25 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e209bbb5ba8b89</t>
+          <t>https://www.indeed.com/viewjob?jk=538c5daa04e61b19</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,94 +4416,94 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1aed5a774867a44</t>
+          <t>https://www.indeed.com/viewjob?jk=ef553cc1ace7891e</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>deviceWISE UI Developer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd4728bf4e081e46</t>
+          <t>https://www.indeed.com/viewjob?jk=5df383ab629f72bf</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Engineer, Digital Products</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NDWA</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Scala, PostgreSQL, ETL, CI/CD</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807809781a081dc7</t>
+          <t>https://www.indeed.com/viewjob?jk=ef8870c8066feaaf</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=538c5daa04e61b19</t>
+          <t>https://www.indeed.com/viewjob?jk=62a4203a1fba28cc</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>IT Labs</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef553cc1ace7891e</t>
+          <t>https://www.indeed.com/viewjob?jk=506839c1bf93a595</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df383ab629f72bf</t>
+          <t>https://www.indeed.com/viewjob?jk=1f05f621fbf0a99e</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef8870c8066feaaf</t>
+          <t>https://www.indeed.com/viewjob?jk=57112973d7d91492</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62a4203a1fba28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=461116607d254fb6</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=506839c1bf93a595</t>
+          <t>https://www.indeed.com/viewjob?jk=6ebcd1a24fe62d4a</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f05f621fbf0a99e</t>
+          <t>https://www.indeed.com/viewjob?jk=de91699c42a4d5df</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Palm Beach, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57112973d7d91492</t>
+          <t>https://www.indeed.com/viewjob?jk=a840871e3ed18bc4</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461116607d254fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=4982f089ec244799</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ebcd1a24fe62d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=23a4a138bbacafd4</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de91699c42a4d5df</t>
+          <t>https://www.indeed.com/viewjob?jk=41fee572c09113fc</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a840871e3ed18bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=8027b829820f9f20</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4982f089ec244799</t>
+          <t>https://www.indeed.com/viewjob?jk=100b43441a6e5d78</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23a4a138bbacafd4</t>
+          <t>https://www.indeed.com/viewjob?jk=6efbcb64de25b825</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fee572c09113fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5fa4a0e40afb12</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8027b829820f9f20</t>
+          <t>https://www.indeed.com/viewjob?jk=2f3e511108bcc51c</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=100b43441a6e5d78</t>
+          <t>https://www.indeed.com/viewjob?jk=1519790fcba6f337</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efbcb64de25b825</t>
+          <t>https://www.indeed.com/viewjob?jk=b1bb6dbdd629fd5d</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5fa4a0e40afb12</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b61c906fad7e9f</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f3e511108bcc51c</t>
+          <t>https://www.indeed.com/viewjob?jk=daa4d10dc3ace6fa</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1519790fcba6f337</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4fcdae47e07839</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1bb6dbdd629fd5d</t>
+          <t>https://www.indeed.com/viewjob?jk=921d23aac4102cbb</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b61c906fad7e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=139395f0e308ecec</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa4d10dc3ace6fa</t>
+          <t>https://www.indeed.com/viewjob?jk=c29e254e300d6a91</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4fcdae47e07839</t>
+          <t>https://www.indeed.com/viewjob?jk=14d5dce121fb7faa</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Sr AI Platform Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=921d23aac4102cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f8d87a308d60fa</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>AI / ML Engineer – Healthcare AI Systems</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139395f0e308ecec</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd6ee1a78b614e0</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Lakebase Sales Specialist, Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29e254e300d6a91</t>
+          <t>https://www.indeed.com/viewjob?jk=aa967f56c6eb5ef3</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Data Engineer (Snowflake, AWS Glue Specialist)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Airflow</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d5dce121fb7faa</t>
+          <t>https://www.indeed.com/viewjob?jk=b40fca841a484a98</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Software Engineer AI/ML</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Scorpion</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Scala, MLOps, MLflow, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e05c14e44f4d784f</t>
+          <t>https://www.indeed.com/viewjob?jk=6ddee5c80e1b050f</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data System Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Scorpion</t>
+          <t>Franciscan Health</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Mishawaka, IN, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ca72623b1ecda0c</t>
+          <t>https://www.indeed.com/viewjob?jk=29a623330902562d</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Engineer (Azure Focus)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Scorpion</t>
+          <t>Blue Ridge Care</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Winchester, VA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Spark, Scala, Snowflake, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b567dc076f197de9</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1ec025d7ae1b86</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Software Engineer AI/ML</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Evendale, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Scala, MLOps, MLflow, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ddee5c80e1b050f</t>
+          <t>https://www.indeed.com/viewjob?jk=0414967af8c69f06</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>AI / ML Engineer – Healthcare AI Systems</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Kafka, SQL Server, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd6ee1a78b614e0</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e1b874414bff22</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist, Healthcare &amp; Life Sciences</t>
+          <t>AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Roche</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa967f56c6eb5ef3</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a65f6db57ee3cc</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>.Net Fullstack Developer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Sidley Austin</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, PostgreSQL, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,357 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0414967af8c69f06</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>eBay</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Tableau, MicroStrategy, CI/CD, Jenkins, GitHub Actions, Jenkins, Git, Python</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b57ff87e9fa89ed9</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>AI Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Roche</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a65f6db57ee3cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>.Net Fullstack Developer</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, PostgreSQL, CI/CD, Azure DevOps, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=0d011c6ed693c14f</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Data Engineer (Snowflake, AWS Glue Specialist)</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Fort Mill, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Airflow</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b40fca841a484a98</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Data System Engineer</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Franciscan Health</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Mishawaka, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29a623330902562d</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Data Engineer (Azure Focus)</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Blue Ridge Care</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Winchester, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1ec025d7ae1b86</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Sr. IT Systems Engineer, AI &amp; Business Solutions</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Dave</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>GCP, BigQuery, Cloud Storage, Scala, Snowflake, ELT, CI/CD, GitHub Actions, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9fd1a88b61bb222e</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Senior Data Solutions Developer</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Commerce</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f28d1a195e234e3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Senior Data Solutions Developer</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Commerce</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Fact Tables, ETL, ELT, Airflow</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00b9a152574ef319</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Java Engineer</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, SQL Server, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e1b874414bff22</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-03.xlsx
+++ b/results/job_matches_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III: Data Engineer</t>
+          <t>Cloud &amp; AI Platform Architect (contract)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6033e89c4de2fb1</t>
+          <t>https://www.indeed.com/viewjob?jk=4035741c18917073</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI Platform Architect (contract)</t>
+          <t>Senior Engineer, AI Data Management</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4035741c18917073</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae6b623863032dc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer, AI Data Management</t>
+          <t>Senior Cloud Engineer (Remote US)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae6b623863032dc</t>
+          <t>https://www.indeed.com/viewjob?jk=3b23c465617e6263</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist - Airvoyant</t>
+          <t>Quant Analytics Associate Sr - DART</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TRAX USA Corp.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f54bacadbab2a4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6bfdcf8cff2c35</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer (Remote US)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b23c465617e6263</t>
+          <t>https://www.indeed.com/viewjob?jk=20490252a7282e6d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Data &amp; Analytics Analyst IV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Emmes Company, LLC</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Redmond, OR, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ab205482e4b0a3</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5018082608c39c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Engineer I, DevOps</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>CareMetx, LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20490252a7282e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f343c9a6ac4261</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Analyst IV</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Redmond, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5018082608c39c</t>
+          <t>https://www.indeed.com/viewjob?jk=37cd157df749b9e8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Engineer I, DevOps</t>
+          <t>Full Stack and AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CareMetx, LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f343c9a6ac4261</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f94b5acff92730</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Varonis Systems</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Azure, Event Hubs, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37cd157df749b9e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d05047e3838d26d9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack and AI Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Lasting Change Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,19 +951,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f94b5acff92730</t>
+          <t>https://www.indeed.com/viewjob?jk=b3a86d1b4b4bd7e7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Varonis Systems</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -972,11 +972,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Event Hubs, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05047e3838d26d9</t>
+          <t>https://www.indeed.com/viewjob?jk=32f15966adb7c80c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Data Engineer - API Platform Engineer - CDH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lasting Change Inc</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3a86d1b4b4bd7e7</t>
+          <t>https://www.indeed.com/viewjob?jk=edb333da77c178b4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32f15966adb7c80c</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc2c674a4afffb4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer - API Platform Engineer - CDH</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edb333da77c178b4</t>
+          <t>https://www.indeed.com/viewjob?jk=dbda51fe27c52909</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Cloud Platform Engineer HYBRID - Cedar Park, TX (Austin area)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>James Avery</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Cedar Park, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Lambda, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc2c674a4afffb4</t>
+          <t>https://www.indeed.com/viewjob?jk=21a782b5d0ec36a3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbda51fe27c52909</t>
+          <t>https://www.indeed.com/viewjob?jk=e6b0d07da6ac2093</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Cloud Platform Engineer HYBRID - Cedar Park, TX (Austin area)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>James Avery</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Nashua, NH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a782b5d0ec36a3</t>
+          <t>https://www.indeed.com/viewjob?jk=70728c10caf53950</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Technical Solutions Architect</t>
+          <t>Senior Data Engineer – Healthcare Data Platforms</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Softchoice</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, GCP, BigQuery, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2514cb3d6eaca2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c87aef812edc38ba</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Nashua, NH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6b0d07da6ac2093</t>
+          <t>https://www.indeed.com/viewjob?jk=324835225383dd25</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Direct Travel</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70728c10caf53950</t>
+          <t>https://www.indeed.com/viewjob?jk=32b2c7b0108f721a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Healthcare Data Platforms</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c87aef812edc38ba</t>
+          <t>https://www.indeed.com/viewjob?jk=7c4f516403858ed9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer - Airvoyant</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Direct Travel</t>
+          <t>TRAX USA Corp.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b2c7b0108f721a</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1046b4cc869c21</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, GCP, BigQuery, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c4f516403858ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=c980ae96d7c71b5b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Airvoyant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TRAX USA Corp.</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MySQL</t>
+          <t>S3, Azure, Cloud Storage, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1046b4cc869c21</t>
+          <t>https://www.indeed.com/viewjob?jk=25b51410dd8ffd88</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD</t>
+          <t>S3, Azure, Cloud Storage, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c980ae96d7c71b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fed518d6fe919b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>IT Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>S3, Azure, Cloud Storage, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b51410dd8ffd88</t>
+          <t>https://www.indeed.com/viewjob?jk=ac62be27b216f151</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineer, Data &amp; AI Infrastructure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>McKinney</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>S3, Azure, Cloud Storage, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, MongoDB, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fed518d6fe919b</t>
+          <t>https://www.indeed.com/viewjob?jk=fad3b7a6b278561a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IT Architect</t>
+          <t>Senior Software Engineer - SRE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac62be27b216f151</t>
+          <t>https://www.indeed.com/viewjob?jk=c48d396577280e6f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48d396577280e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f8a17e02da010e4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Senior Full Stack JS Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f8a17e02da010e4</t>
+          <t>https://www.indeed.com/viewjob?jk=ff84a48bf7f2b214</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff84a48bf7f2b214</t>
+          <t>https://www.indeed.com/viewjob?jk=2a341fbae4ab3a40</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a341fbae4ab3a40</t>
+          <t>https://www.indeed.com/viewjob?jk=2d370271ca54d590</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d370271ca54d590</t>
+          <t>https://www.indeed.com/viewjob?jk=8dc0480a620e54b0</t>
         </is>
       </c>
     </row>
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dc0480a620e54b0</t>
+          <t>https://www.indeed.com/viewjob?jk=aa8f514248ec1f9f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Full Stack JS Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa8f514248ec1f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=2907e0725b12b84d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Spark, Scala, Kafka, Talend, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2907e0725b12b84d</t>
+          <t>https://www.indeed.com/viewjob?jk=09530a3bb367b138</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer - Ad Platform (Audience Team)</t>
+          <t>Data Layer Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SOSi</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, S3, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f108b3fa1b3553</t>
+          <t>https://www.indeed.com/viewjob?jk=e045fbd4ef10a7c1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer (contract)</t>
+          <t>Cloud Data Platform Engineer - Remote</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Spark, Scala, Kafka, Talend, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09530a3bb367b138</t>
+          <t>https://www.indeed.com/viewjob?jk=dea777f331fdeff3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Layer Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SOSi</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e045fbd4ef10a7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=837c797913f92786</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer - Remote</t>
+          <t>Senior Data Engineer (Microsoft Fabric, Power BI)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Kimball, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea777f331fdeff3</t>
+          <t>https://www.indeed.com/viewjob?jk=0500d4e766982809</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DATA ANALYST L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL</t>
+          <t>AWS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Jenkins, Jenkins, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837c797913f92786</t>
+          <t>https://www.indeed.com/viewjob?jk=b65dda35913c82cc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric, Power BI)</t>
+          <t>Analytics Software Engineer IV</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Kimball, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Spark, PySpark, Scala, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0500d4e766982809</t>
+          <t>https://www.indeed.com/viewjob?jk=93d71aec8bc25826</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Analytics Software Engineer IV</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Ceresti Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2096,29 +2096,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Spark, PySpark, Scala, Tableau, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Spark, PostgreSQL, Data Modeling, Kimball, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d71aec8bc25826</t>
+          <t>https://www.indeed.com/viewjob?jk=94bd4f4546ea6e61</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Multiple Levels)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ceresti Health</t>
+          <t>Astrana Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PostgreSQL, Data Modeling, Kimball, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94bd4f4546ea6e61</t>
+          <t>https://www.indeed.com/viewjob?jk=4c749a4ea9071424</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b02ec8d04b37bb</t>
+          <t>https://www.indeed.com/viewjob?jk=564f104de61b3f0a</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=213170f837efaaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=69b02ec8d04b37bb</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Cloud Technical Architect</t>
+          <t>Senior Data Modeler</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Davidson, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Cloud Storage, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb363572dc01c51e</t>
+          <t>https://www.indeed.com/viewjob?jk=745e80023e3ea1c3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr AI Platform Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Snowflake, Time Travel, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e01343345f387b3</t>
+          <t>https://www.indeed.com/viewjob?jk=213170f837efaaa7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Modeler</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Davidson, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745e80023e3ea1c3</t>
+          <t>https://www.indeed.com/viewjob?jk=4a585d9e5f8d2b5e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Sr AI Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Snowflake, Time Travel, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a585d9e5f8d2b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e01343345f387b3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e209bbb5ba8b89</t>
+          <t>https://www.indeed.com/viewjob?jk=e915b96bc735537f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1aed5a774867a44</t>
+          <t>https://www.indeed.com/viewjob?jk=79885c5e8fab39db</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Consultant - GenAI Full Stack Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nabis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Arlington Heights, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e75782fef7c9f07</t>
+          <t>https://www.indeed.com/viewjob?jk=001f952456c68ada</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e915b96bc735537f</t>
+          <t>https://www.indeed.com/viewjob?jk=485a39269b2e3d4d</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79885c5e8fab39db</t>
+          <t>https://www.indeed.com/viewjob?jk=58cc27c0cbb47bac</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Williamsville, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=001f952456c68ada</t>
+          <t>https://www.indeed.com/viewjob?jk=87cbeb2e241685bf</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485a39269b2e3d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=71ef27b9394116e2</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58cc27c0cbb47bac</t>
+          <t>https://www.indeed.com/viewjob?jk=75b011e6183a3001</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87cbeb2e241685bf</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5e75b883628be8</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ef27b9394116e2</t>
+          <t>https://www.indeed.com/viewjob?jk=3f21eb9abbc06424</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b011e6183a3001</t>
+          <t>https://www.indeed.com/viewjob?jk=7eef869318dd1c6a</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5e75b883628be8</t>
+          <t>https://www.indeed.com/viewjob?jk=634538fd6c2620be</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f21eb9abbc06424</t>
+          <t>https://www.indeed.com/viewjob?jk=14d36f89aa2f5055</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eef869318dd1c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=11f4552ef8c93f53</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634538fd6c2620be</t>
+          <t>https://www.indeed.com/viewjob?jk=b5725cf97c1aa655</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d36f89aa2f5055</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf36a15d0917596</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11f4552ef8c93f53</t>
+          <t>https://www.indeed.com/viewjob?jk=61ed14faf1c28e26</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5725cf97c1aa655</t>
+          <t>https://www.indeed.com/viewjob?jk=885299bf1d26ab0b</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf36a15d0917596</t>
+          <t>https://www.indeed.com/viewjob?jk=d5ef65a00a253424</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61ed14faf1c28e26</t>
+          <t>https://www.indeed.com/viewjob?jk=74f1c7a929a74260</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885299bf1d26ab0b</t>
+          <t>https://www.indeed.com/viewjob?jk=e2cf14047ca54bfa</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5ef65a00a253424</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d980516553b2ed</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f1c7a929a74260</t>
+          <t>https://www.indeed.com/viewjob?jk=1276f9e51c745c4b</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2cf14047ca54bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=4132ea5087b63157</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d980516553b2ed</t>
+          <t>https://www.indeed.com/viewjob?jk=353af706a091ac66</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1276f9e51c745c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=2df59d5f09858a51</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4132ea5087b63157</t>
+          <t>https://www.indeed.com/viewjob?jk=195f6f0f31e468f4</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353af706a091ac66</t>
+          <t>https://www.indeed.com/viewjob?jk=6c0116b2843f1783</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2df59d5f09858a51</t>
+          <t>https://www.indeed.com/viewjob?jk=89094576beb673fb</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=195f6f0f31e468f4</t>
+          <t>https://www.indeed.com/viewjob?jk=afd8553ecac5c59a</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c0116b2843f1783</t>
+          <t>https://www.indeed.com/viewjob?jk=049cd79cca059ec2</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89094576beb673fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f858cd1793a72366</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd8553ecac5c59a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ff73add21b8411</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=049cd79cca059ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=d5295e1f0b20718a</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f858cd1793a72366</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5e91473b3c36e</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ff73add21b8411</t>
+          <t>https://www.indeed.com/viewjob?jk=8ecbd64a6ca110fb</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5295e1f0b20718a</t>
+          <t>https://www.indeed.com/viewjob?jk=39d251ef38eb8cbe</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5e91473b3c36e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac3b2b8fbc8d7f27</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ecbd64a6ca110fb</t>
+          <t>https://www.indeed.com/viewjob?jk=db764d6511c61ed6</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d251ef38eb8cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0dda829168270c</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3b2b8fbc8d7f27</t>
+          <t>https://www.indeed.com/viewjob?jk=4273beebb8ab17d1</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db764d6511c61ed6</t>
+          <t>https://www.indeed.com/viewjob?jk=29a3244ce3bcc7b7</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0dda829168270c</t>
+          <t>https://www.indeed.com/viewjob?jk=03e209bbb5ba8b89</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273beebb8ab17d1</t>
+          <t>https://www.indeed.com/viewjob?jk=a1aed5a774867a44</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nabis</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a3244ce3bcc7b7</t>
+          <t>https://www.indeed.com/viewjob?jk=7e75782fef7c9f07</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4388,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer (Oracle)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef553cc1ace7891e</t>
+          <t>https://www.indeed.com/viewjob?jk=b698f84637b7e148</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df383ab629f72bf</t>
+          <t>https://www.indeed.com/viewjob?jk=ef553cc1ace7891e</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef8870c8066feaaf</t>
+          <t>https://www.indeed.com/viewjob?jk=5518f07c3a7fbfc2</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62a4203a1fba28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=0219ec8577fe8e4c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Sr AI Platform Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=506839c1bf93a595</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f8d87a308d60fa</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Lakebase Sales Specialist, Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f05f621fbf0a99e</t>
+          <t>https://www.indeed.com/viewjob?jk=aa967f56c6eb5ef3</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>AI / ML Engineer – Healthcare AI Systems</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Palm Beach, FL, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57112973d7d91492</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd6ee1a78b614e0</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Data Engineer (Snowflake, AWS Glue Specialist)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Airflow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461116607d254fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=b40fca841a484a98</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Software Engineer AI/ML</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Evendale, OH, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Scala, MLOps, MLflow, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ebcd1a24fe62d4a</t>
+          <t>https://www.indeed.com/viewjob?jk=6ddee5c80e1b050f</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Data System Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Franciscan Health</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Mishawaka, IN, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de91699c42a4d5df</t>
+          <t>https://www.indeed.com/viewjob?jk=29a623330902562d</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Data Engineer (Azure Focus)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Blue Ridge Care</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Winchester, VA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a840871e3ed18bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1ec025d7ae1b86</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4982f089ec244799</t>
+          <t>https://www.indeed.com/viewjob?jk=0414967af8c69f06</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Kafka, SQL Server, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23a4a138bbacafd4</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e1b874414bff22</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>Roche</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fee572c09113fc</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a65f6db57ee3cc</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>.Net Fullstack Developer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>IT Labs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, PostgreSQL, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4905,846 +4905,6 @@
         </is>
       </c>
       <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8027b829820f9f20</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=100b43441a6e5d78</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6efbcb64de25b825</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5fa4a0e40afb12</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f3e511108bcc51c</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1519790fcba6f337</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b1bb6dbdd629fd5d</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b61c906fad7e9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=daa4d10dc3ace6fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4fcdae47e07839</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=921d23aac4102cbb</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=139395f0e308ecec</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c29e254e300d6a91</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Senior Azure DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>IT Labs</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Memphis, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14d5dce121fb7faa</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Sr AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Appex Innovation</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f8d87a308d60fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>AI / ML Engineer – Healthcare AI Systems</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Expleo Group</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Rochester, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, MLOps, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd6ee1a78b614e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Lakebase Sales Specialist, Healthcare &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Central, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa967f56c6eb5ef3</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Data Engineer (Snowflake, AWS Glue Specialist)</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Fort Mill, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Airflow</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b40fca841a484a98</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Software Engineer AI/ML</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>GE Aerospace</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Scala, MLOps, MLflow, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ddee5c80e1b050f</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Data System Engineer</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Franciscan Health</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Mishawaka, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29a623330902562d</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Data Engineer (Azure Focus)</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Blue Ridge Care</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Winchester, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1ec025d7ae1b86</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Sidley Austin</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0414967af8c69f06</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Java Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, SQL Server, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e1b874414bff22</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>AI Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Roche</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a65f6db57ee3cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>.Net Fullstack Developer</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, PostgreSQL, CI/CD, Azure DevOps, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0d011c6ed693c14f</t>
         </is>

--- a/results/job_matches_2026-06-03.xlsx
+++ b/results/job_matches_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI Platform Architect (contract)</t>
+          <t>Senior Engineer, AI Data Management</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4035741c18917073</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae6b623863032dc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Engineer, AI Data Management</t>
+          <t>Senior Cloud Engineer (Remote US)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae6b623863032dc</t>
+          <t>https://www.indeed.com/viewjob?jk=3b23c465617e6263</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer (Remote US)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b23c465617e6263</t>
+          <t>https://www.indeed.com/viewjob?jk=20490252a7282e6d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Quant Analytics Associate Sr - DART</t>
+          <t>Data &amp; Analytics Analyst IV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Redmond, OR, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6bfdcf8cff2c35</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5018082608c39c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Engineer I, DevOps</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>CareMetx, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20490252a7282e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=f1f343c9a6ac4261</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Analyst IV</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Redmond, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5018082608c39c</t>
+          <t>https://www.indeed.com/viewjob?jk=37cd157df749b9e8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer I, DevOps</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CareMetx, LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f343c9a6ac4261</t>
+          <t>https://www.indeed.com/viewjob?jk=eba11dc550c0d956</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37cd157df749b9e8</t>
+          <t>https://www.indeed.com/viewjob?jk=eea1d0eeb00ba384</t>
         </is>
       </c>
     </row>
@@ -888,52 +888,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Varonis Systems</t>
+          <t>Anteriad</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Event Hubs, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Google Cloud Platform, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05047e3838d26d9</t>
+          <t>https://www.indeed.com/viewjob?jk=5a53981dcd494255</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Sr. Software Engineer II (DevOps)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lasting Change Inc</t>
+          <t>Hi Marley</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3a86d1b4b4bd7e7</t>
+          <t>https://www.indeed.com/viewjob?jk=57e6ba06d3a7b30f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Applied Information Sciences</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32f15966adb7c80c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4d756dafb24330</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer - API Platform Engineer - CDH</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Lasting Change Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edb333da77c178b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3a86d1b4b4bd7e7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc2c674a4afffb4</t>
+          <t>https://www.indeed.com/viewjob?jk=32f15966adb7c80c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - API Platform Engineer - CDH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbda51fe27c52909</t>
+          <t>https://www.indeed.com/viewjob?jk=edb333da77c178b4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Cloud Platform Engineer HYBRID - Cedar Park, TX (Austin area)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>James Avery</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a782b5d0ec36a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e6b0d07da6ac2093</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6b0d07da6ac2093</t>
+          <t>https://www.indeed.com/viewjob?jk=7433f9b8b5c4a5a6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70728c10caf53950</t>
+          <t>https://www.indeed.com/viewjob?jk=ddf7449abdd32b05</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Healthcare Data Platforms</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Nashua, NH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, GCP, BigQuery, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c87aef812edc38ba</t>
+          <t>https://www.indeed.com/viewjob?jk=70728c10caf53950</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – Healthcare Data Platforms</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, GCP, BigQuery, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324835225383dd25</t>
+          <t>https://www.indeed.com/viewjob?jk=c87aef812edc38ba</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Direct Travel</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashua, NH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b2c7b0108f721a</t>
+          <t>https://www.indeed.com/viewjob?jk=324835225383dd25</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Direct Travel</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, GCP, BigQuery, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c4f516403858ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=32b2c7b0108f721a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Airvoyant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TRAX USA Corp.</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, GCP, BigQuery, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1046b4cc869c21</t>
+          <t>https://www.indeed.com/viewjob?jk=7c4f516403858ed9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Full Stack Developer - Airvoyant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>TRAX USA Corp.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c980ae96d7c71b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1046b4cc869c21</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, ML Platform | Parafin</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>carnaby fox</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>S3, Azure, Cloud Storage, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b51410dd8ffd88</t>
+          <t>https://www.indeed.com/viewjob?jk=4377663fa2ea1245</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Noise Consulting Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>S3, Azure, Cloud Storage, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fed518d6fe919b</t>
+          <t>https://www.indeed.com/viewjob?jk=2baa480224d46766</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IT Architect</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac62be27b216f151</t>
+          <t>https://www.indeed.com/viewjob?jk=c980ae96d7c71b5b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Data &amp; AI Infrastructure</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>McKinney</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, MongoDB, ELT, CI/CD</t>
+          <t>S3, Azure, Cloud Storage, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad3b7a6b278561a</t>
+          <t>https://www.indeed.com/viewjob?jk=25b51410dd8ffd88</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
+          <t>S3, Azure, Cloud Storage, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48d396577280e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5fed518d6fe919b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Senior BI Analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Walker &amp; Dunlop</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f8a17e02da010e4</t>
+          <t>https://www.indeed.com/viewjob?jk=827ebbc8cea913b8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Full Stack JS Engineer</t>
+          <t>Senior Platform Engineer, Data &amp; AI Infrastructure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>McKinney</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, MongoDB, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff84a48bf7f2b214</t>
+          <t>https://www.indeed.com/viewjob?jk=fad3b7a6b278561a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack JS Engineer</t>
+          <t>IT Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,29 +1676,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a341fbae4ab3a40</t>
+          <t>https://www.indeed.com/viewjob?jk=ac62be27b216f151</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Full Stack JS Engineer</t>
+          <t>Senior Software Engineer - SRE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>OneTrust</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d370271ca54d590</t>
+          <t>https://www.indeed.com/viewjob?jk=c48d396577280e6f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Full Stack JS Engineer</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,42 +1756,42 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dc0480a620e54b0</t>
+          <t>https://www.indeed.com/viewjob?jk=0f8a17e02da010e4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Full Stack JS Engineer</t>
+          <t>Software Development Engineer â€“ Backend / Platform</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>Kinesis, IAM, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa8f514248ec1f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=41a635808e4af271</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Architect: Enterprise Data</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Mayer Brown LLP</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837c797913f92786</t>
+          <t>https://www.indeed.com/viewjob?jk=7d1633dd04465309</t>
         </is>
       </c>
     </row>
@@ -2043,12 +2043,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analytics Software Engineer IV</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Ceresti Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Spark, PySpark, Scala, Tableau, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Spark, PostgreSQL, Data Modeling, Kimball, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d71aec8bc25826</t>
+          <t>https://www.indeed.com/viewjob?jk=94bd4f4546ea6e61</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Informatica ETL Developer - 6326296</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ceresti Health</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PostgreSQL, Data Modeling, Kimball, dbt, CI/CD, Airflow</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94bd4f4546ea6e61</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a17c04578e9be3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer (Multiple Levels)</t>
+          <t>Informatica ETL Developer - 6326296</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Astrana Health</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Star Schema, Snowflake Schema</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c749a4ea9071424</t>
+          <t>https://www.indeed.com/viewjob?jk=21eab84e17f0b1ac</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>General Intuition &amp; Medal</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235e8563d0407abd</t>
+          <t>https://www.indeed.com/viewjob?jk=564f104de61b3f0a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Site Reliability / Infrastructure Engineer</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd6b80058693cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=0a083efe79b22465</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Exostar</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9043dd14b9a4d11b</t>
+          <t>https://www.indeed.com/viewjob?jk=233d27bbc07fd70f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564f104de61b3f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=252de2ad1a0af01a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c25c1b0bc5a8d73</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1b5426a6197ba8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b02ec8d04b37bb</t>
+          <t>https://www.indeed.com/viewjob?jk=3c25c1b0bc5a8d73</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Modeler</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Davidson, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745e80023e3ea1c3</t>
+          <t>https://www.indeed.com/viewjob?jk=213170f837efaaa7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>Safelease</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=213170f837efaaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=6884b300f1b32ae4</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Full Stack Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Akanksha LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, Lambda, API Gateway, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e915b96bc735537f</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf16acc114cd913</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79885c5e8fab39db</t>
+          <t>https://www.indeed.com/viewjob?jk=03e209bbb5ba8b89</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=001f952456c68ada</t>
+          <t>https://www.indeed.com/viewjob?jk=a1aed5a774867a44</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485a39269b2e3d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=69b02ec8d04b37bb</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nabis</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58cc27c0cbb47bac</t>
+          <t>https://www.indeed.com/viewjob?jk=7e75782fef7c9f07</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Williamsville, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87cbeb2e241685bf</t>
+          <t>https://www.indeed.com/viewjob?jk=538c5daa04e61b19</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Data Engineer (Oracle)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ef27b9394116e2</t>
+          <t>https://www.indeed.com/viewjob?jk=b698f84637b7e148</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b011e6183a3001</t>
+          <t>https://www.indeed.com/viewjob?jk=ef553cc1ace7891e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Redshift, Databricks, BigQuery, Spark, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5e75b883628be8</t>
+          <t>https://www.indeed.com/viewjob?jk=90a874d216618930</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f21eb9abbc06424</t>
+          <t>https://www.indeed.com/viewjob?jk=5518f07c3a7fbfc2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eef869318dd1c6a</t>
+          <t>https://www.indeed.com/viewjob?jk=0219ec8577fe8e4c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Sr AI Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634538fd6c2620be</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f8d87a308d60fa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Lakebase Sales Specialist, Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d36f89aa2f5055</t>
+          <t>https://www.indeed.com/viewjob?jk=aa967f56c6eb5ef3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Data Engineer (Snowflake, AWS Glue Specialist)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,67 +3261,67 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11f4552ef8c93f53</t>
+          <t>https://www.indeed.com/viewjob?jk=b40fca841a484a98</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>AI Software Engineer - Center for Diagnostics and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cleveland Clinic</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>S3, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5725cf97c1aa655</t>
+          <t>https://www.indeed.com/viewjob?jk=10aaff122c10f274</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Software Engineer AI/ML</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Evendale, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Scala, MLOps, MLflow, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf36a15d0917596</t>
+          <t>https://www.indeed.com/viewjob?jk=6ddee5c80e1b050f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Data System Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Franciscan Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Mishawaka, IN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61ed14faf1c28e26</t>
+          <t>https://www.indeed.com/viewjob?jk=29a623330902562d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885299bf1d26ab0b</t>
+          <t>https://www.indeed.com/viewjob?jk=0414967af8c69f06</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, SQL Server, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5ef65a00a253424</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e1b874414bff22</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Roche</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f1c7a929a74260</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a65f6db57ee3cc</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
+          <t>.Net Fullstack Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, Azure, PostgreSQL, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3505,1406 +3505,6 @@
         </is>
       </c>
       <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2cf14047ca54bfa</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d980516553b2ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1276f9e51c745c4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4132ea5087b63157</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=353af706a091ac66</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2df59d5f09858a51</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=195f6f0f31e468f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c0116b2843f1783</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Grand Rapids, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=89094576beb673fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afd8553ecac5c59a</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=049cd79cca059ec2</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f858cd1793a72366</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ff73add21b8411</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Davenport, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d5295e1f0b20718a</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5e91473b3c36e</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Fresno, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ecbd64a6ca110fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39d251ef38eb8cbe</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac3b2b8fbc8d7f27</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db764d6511c61ed6</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0dda829168270c</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4273beebb8ab17d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Consultant - GenAI Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Cloud Storage, Vertex AI, Scala, ETL, Docker</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29a3244ce3bcc7b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03e209bbb5ba8b89</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1aed5a774867a44</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Nabis</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e75782fef7c9f07</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Solutions Architect - AI</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Five Below</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=538c5daa04e61b19</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer (Oracle)</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Bitscopic</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b698f84637b7e148</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>AMH</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Draper, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef553cc1ace7891e</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Kirkland &amp; Ellis</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5518f07c3a7fbfc2</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Kirkland &amp; Ellis</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0219ec8577fe8e4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Sr AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Appex Innovation</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f8d87a308d60fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Lakebase Sales Specialist, Healthcare &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Central, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa967f56c6eb5ef3</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>AI / ML Engineer – Healthcare AI Systems</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Expleo Group</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Rochester, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, MLOps, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd6ee1a78b614e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Data Engineer (Snowflake, AWS Glue Specialist)</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Fort Mill, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Airflow</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b40fca841a484a98</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Software Engineer AI/ML</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>GE Aerospace</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Evendale, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Scala, MLOps, MLflow, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ddee5c80e1b050f</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Data System Engineer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Franciscan Health</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Mishawaka, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29a623330902562d</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Data Engineer (Azure Focus)</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Blue Ridge Care</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Winchester, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1ec025d7ae1b86</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Sidley Austin</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0414967af8c69f06</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Java Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, SQL Server, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e1b874414bff22</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>AI Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Roche</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a65f6db57ee3cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>.Net Fullstack Developer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, PostgreSQL, CI/CD, Azure DevOps, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0d011c6ed693c14f</t>
         </is>

--- a/results/job_matches_2026-06-03.xlsx
+++ b/results/job_matches_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - API Platform Engineer - CDH</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>IKS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Hive, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d846903d81c33e82</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6b03669fcb256f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ETL/ELT Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IKS Health</t>
+          <t>AEM Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,21 +517,21 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6b03669fcb256f</t>
+          <t>https://www.indeed.com/viewjob?jk=a4c2c00b592047da</t>
         </is>
       </c>
     </row>
@@ -608,117 +608,117 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer (Remote US)</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b23c465617e6263</t>
+          <t>https://www.indeed.com/viewjob?jk=b9f4e94883170da4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20490252a7282e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=feaf489696c6ebd7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Analyst IV</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Redmond, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5018082608c39c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac18de92e2d0da2c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer I, DevOps</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CareMetx, LLC</t>
+          <t>Tunnl</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,151 +727,151 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f343c9a6ac4261</t>
+          <t>https://www.indeed.com/viewjob?jk=b66532c29a2d2fb3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37cd157df749b9e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d784ad2795e0379d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Cloud Engineer (Remote US)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba11dc550c0d956</t>
+          <t>https://www.indeed.com/viewjob?jk=3b23c465617e6263</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea1d0eeb00ba384</t>
+          <t>https://www.indeed.com/viewjob?jk=20490252a7282e6d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack and AI Engineer</t>
+          <t>Data &amp; Analytics Analyst IV</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Redmond, OR, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f94b5acff92730</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5018082608c39c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Gen AI Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Anteriad</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Google Cloud Platform, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, S3, Azure, Data Lake Storage, Spark, Kafka, Oracle, ELT, dbt, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a53981dcd494255</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfe18dbf4b291f3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II (DevOps)</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hi Marley</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, DynamoDB, ETL, ELT</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e6ba06d3a7b30f</t>
+          <t>https://www.indeed.com/viewjob?jk=37cd157df749b9e8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Applied Information Sciences</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4d756dafb24330</t>
+          <t>https://www.indeed.com/viewjob?jk=eba11dc550c0d956</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lasting Change Inc</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3a86d1b4b4bd7e7</t>
+          <t>https://www.indeed.com/viewjob?jk=eea1d0eeb00ba384</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32f15966adb7c80c</t>
+          <t>https://www.indeed.com/viewjob?jk=336bfe0af38918a1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer - API Platform Engineer - CDH</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>SIGNITIVES</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edb333da77c178b4</t>
+          <t>https://www.indeed.com/viewjob?jk=afef76c3c4cb302e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Anteriad</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Google Cloud Platform, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6b0d07da6ac2093</t>
+          <t>https://www.indeed.com/viewjob?jk=5a53981dcd494255</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer II (DevOps)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Hi Marley</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7433f9b8b5c4a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=57e6ba06d3a7b30f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Applied Information Sciences</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddf7449abdd32b05</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4d756dafb24330</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Lasting Change Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70728c10caf53950</t>
+          <t>https://www.indeed.com/viewjob?jk=b3a86d1b4b4bd7e7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Healthcare Data Platforms</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, GCP, BigQuery, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c87aef812edc38ba</t>
+          <t>https://www.indeed.com/viewjob?jk=32f15966adb7c80c</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324835225383dd25</t>
+          <t>https://www.indeed.com/viewjob?jk=7433f9b8b5c4a5a6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Direct Travel</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b2c7b0108f721a</t>
+          <t>https://www.indeed.com/viewjob?jk=ddf7449abdd32b05</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Nashua, NH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, GCP, BigQuery, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c4f516403858ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=70728c10caf53950</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Airvoyant</t>
+          <t>Senior Data Engineer – Healthcare Data Platforms</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TRAX USA Corp.</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, GCP, BigQuery, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1046b4cc869c21</t>
+          <t>https://www.indeed.com/viewjob?jk=c87aef812edc38ba</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, ML Platform | Parafin</t>
+          <t>Full Stack Developer - Airvoyant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>carnaby fox</t>
+          <t>TRAX USA Corp.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4377663fa2ea1245</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1046b4cc869c21</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer - III</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Noise Consulting Group</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Snowflake, PostgreSQL, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2baa480224d46766</t>
+          <t>https://www.indeed.com/viewjob?jk=a5cff3964beedb24</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Engineer, ML Platform | Parafin</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>carnaby fox</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c980ae96d7c71b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=4377663fa2ea1245</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - III</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Noise Consulting Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>S3, Azure, Cloud Storage, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b51410dd8ffd88</t>
+          <t>https://www.indeed.com/viewjob?jk=2baa480224d46766</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>S3, Azure, Cloud Storage, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5fed518d6fe919b</t>
+          <t>https://www.indeed.com/viewjob?jk=c980ae96d7c71b5b</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Data &amp; AI Infrastructure</t>
+          <t>AWS Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>McKinney</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, MongoDB, ELT, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad3b7a6b278561a</t>
+          <t>https://www.indeed.com/viewjob?jk=723c6fbf1e8f4749</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IT Architect</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Artisan Studios, LLC DBA Amy Howard At Home &amp; A Makers' Studio</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Spark, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac62be27b216f151</t>
+          <t>https://www.indeed.com/viewjob?jk=7350027af6d67644</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OneTrust</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, CI/CD, Jenkins, Terraform, Kubernetes, AKS</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48d396577280e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=34430b584944faaf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,42 +1746,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f8a17e02da010e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a988b9cc3e868674</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Development Engineer â€“ Backend / Platform</t>
+          <t>Senior Platform Engineer, Data &amp; AI Infrastructure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>McKinney</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, MongoDB, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a635808e4af271</t>
+          <t>https://www.indeed.com/viewjob?jk=fad3b7a6b278561a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Software Development Engineer â€“ Backend / Platform</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>Kinesis, IAM, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2907e0725b12b84d</t>
+          <t>https://www.indeed.com/viewjob?jk=41a635808e4af271</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Layer Engineer</t>
+          <t>Cloud Data Platform Engineer - Remote</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SOSi</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e045fbd4ef10a7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=dea777f331fdeff3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer - Remote</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea777f331fdeff3</t>
+          <t>https://www.indeed.com/viewjob?jk=47eb49ae40d3103f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Architect: Enterprise Data</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mayer Brown LLP</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1633dd04465309</t>
+          <t>https://www.indeed.com/viewjob?jk=837b89c39e0b1f1d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric, Power BI)</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,139 +1991,139 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Kimball, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0500d4e766982809</t>
+          <t>https://www.indeed.com/viewjob?jk=101a2c6e0c8a3069</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DATA ANALYST L3(CONTRACT)</t>
+          <t>Application Architect (contract)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Spark, Scala, Kafka, Jenkins, Jenkins, Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65dda35913c82cc</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c4dc6b11200157</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Contact Center Architect – Healthcare &amp; Amazon Connect – R01566032</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ceresti Health</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PostgreSQL, Data Modeling, Kimball, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94bd4f4546ea6e61</t>
+          <t>https://www.indeed.com/viewjob?jk=baab0523b145fc75</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Informatica ETL Developer - 6326296</t>
+          <t>Senior Data Engineer (Microsoft Fabric, Power BI)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Kimball, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a17c04578e9be3</t>
+          <t>https://www.indeed.com/viewjob?jk=0500d4e766982809</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Informatica ETL Developer - 6326296</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, SQS, API Gateway, ECS, RDS, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21eab84e17f0b1ac</t>
+          <t>https://www.indeed.com/viewjob?jk=e888182752c6207b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Informatica ETL Developer - 6326296</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Ceresti Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
+          <t>AWS, S3, RDS, Spark, PostgreSQL, Data Modeling, Kimball, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40516db2dcf106b5</t>
+          <t>https://www.indeed.com/viewjob?jk=94bd4f4546ea6e61</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Informatica ETL Developer - 6326296</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fashion Nova</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Beverly Hills, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, dbt, CI/CD, Airflow</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80f5d754f1ffd13</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a17c04578e9be3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Informatica ETL Developer - 6326296</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, CI/CD, Terraform, Airflow</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8841e4e75fbe68</t>
+          <t>https://www.indeed.com/viewjob?jk=21eab84e17f0b1ac</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Informatica ETL Developer - 6326296</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ca03311ac42217</t>
+          <t>https://www.indeed.com/viewjob?jk=40516db2dcf106b5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9faea0d55a841c9</t>
+          <t>https://www.indeed.com/viewjob?jk=564f104de61b3f0a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2abbc5f73ae2028d</t>
+          <t>https://www.indeed.com/viewjob?jk=1849a5b7a2f2af9b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Safelease</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33de66454718a7f8</t>
+          <t>https://www.indeed.com/viewjob?jk=6884b300f1b32ae4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96d64f561456df6</t>
+          <t>https://www.indeed.com/viewjob?jk=213170f837efaaa7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Full Stack Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>The Akanksha LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564f104de61b3f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf16acc114cd913</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=252de2ad1a0af01a</t>
+          <t>https://www.indeed.com/viewjob?jk=3c25c1b0bc5a8d73</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1b5426a6197ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=03e209bbb5ba8b89</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c25c1b0bc5a8d73</t>
+          <t>https://www.indeed.com/viewjob?jk=a1aed5a774867a44</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=213170f837efaaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=69b02ec8d04b37bb</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Safelease</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6884b300f1b32ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3c84e2687fbb09</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a585d9e5f8d2b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=538c5daa04e61b19</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr AI Platform Engineer</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Snowflake, Time Travel, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e01343345f387b3</t>
+          <t>https://www.indeed.com/viewjob?jk=bb44a4b768419ca2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Cloud Engineer</t>
+          <t>Senior Data Engineer (Oracle)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Akanksha LLC</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,164 +2806,164 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf16acc114cd913</t>
+          <t>https://www.indeed.com/viewjob?jk=b698f84637b7e148</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e209bbb5ba8b89</t>
+          <t>https://www.indeed.com/viewjob?jk=d604ebca572d9a0d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1aed5a774867a44</t>
+          <t>https://www.indeed.com/viewjob?jk=244f96a693bca9f8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b02ec8d04b37bb</t>
+          <t>https://www.indeed.com/viewjob?jk=4229f7f9f0a4e0f7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Technical Scrum Master</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nabis</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e75782fef7c9f07</t>
+          <t>https://www.indeed.com/viewjob?jk=3405192fd1717731</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Natera</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,29 +2971,29 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, RDS, Spark, Scala, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=538c5daa04e61b19</t>
+          <t>https://www.indeed.com/viewjob?jk=14d57e3def97a538</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Oracle)</t>
+          <t>Lakebase Sales Specialist- Financial Services</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b698f84637b7e148</t>
+          <t>https://www.indeed.com/viewjob?jk=6d86224c98360290</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>Redshift, Databricks, BigQuery, Spark, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef553cc1ace7891e</t>
+          <t>https://www.indeed.com/viewjob?jk=90a874d216618930</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a874d216618930</t>
+          <t>https://www.indeed.com/viewjob?jk=5518f07c3a7fbfc2</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5518f07c3a7fbfc2</t>
+          <t>https://www.indeed.com/viewjob?jk=0219ec8577fe8e4c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Sr AI Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0219ec8577fe8e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f8d87a308d60fa</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr AI Platform Engineer</t>
+          <t>Lakebase Sales Specialist, Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f8d87a308d60fa</t>
+          <t>https://www.indeed.com/viewjob?jk=aa967f56c6eb5ef3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist, Healthcare &amp; Life Sciences</t>
+          <t>AI Software Engineer - Center for Diagnostics and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cleveland Clinic</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>S3, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa967f56c6eb5ef3</t>
+          <t>https://www.indeed.com/viewjob?jk=10aaff122c10f274</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, AWS Glue Specialist)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, Airflow</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b40fca841a484a98</t>
+          <t>https://www.indeed.com/viewjob?jk=0414967af8c69f06</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Center for Diagnostics and Artificial Intelligence</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cleveland Clinic</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, SQL Server, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10aaff122c10f274</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e1b874414bff22</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer AI/ML</t>
+          <t>AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Roche</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Evendale, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Scala, MLOps, MLflow, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,182 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ddee5c80e1b050f</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Data System Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Franciscan Health</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Mishawaka, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29a623330902562d</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Sidley Austin</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0414967af8c69f06</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Java Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, SQL Server, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e1b874414bff22</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>AI Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Roche</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=e5a65f6db57ee3cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>.Net Fullstack Developer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, Azure, PostgreSQL, CI/CD, Azure DevOps, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d011c6ed693c14f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-03.xlsx
+++ b/results/job_matches_2026-06-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,12 +491,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6b03669fcb256f</t>
+          <t>https://www.indeed.com/viewjob?jk=f18524a0d1c2e02e</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Sr. AWS Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9f4e94883170da4</t>
+          <t>https://www.indeed.com/viewjob?jk=d62532bd79c16947</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaf489696c6ebd7</t>
+          <t>https://www.indeed.com/viewjob?jk=b9f4e94883170da4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac18de92e2d0da2c</t>
+          <t>https://www.indeed.com/viewjob?jk=feaf489696c6ebd7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tunnl</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB, Splunk</t>
+          <t>AWS, Glue, Redshift, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66532c29a2d2fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=ac18de92e2d0da2c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tunnl</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d784ad2795e0379d</t>
+          <t>https://www.indeed.com/viewjob?jk=b66532c29a2d2fb3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer (Remote US)</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b23c465617e6263</t>
+          <t>https://www.indeed.com/viewjob?jk=d784ad2795e0379d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Cloud Engineer (Remote US)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, YARN, Spark</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, GCP, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20490252a7282e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=3b23c465617e6263</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Analyst IV</t>
+          <t>Full Stack Software Engineer, Security &amp; Information Technology - USDS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Redmond, OR, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5018082608c39c</t>
+          <t>https://www.indeed.com/viewjob?jk=b8131bdacb963c45</t>
         </is>
       </c>
     </row>
@@ -923,52 +923,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Developer</t>
+          <t>Senior Developer I - Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Azure, Spark, Scala, Kafka, Polars, Snowflake, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37cd157df749b9e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e3803b26dd25a2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior IT Big Data Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba11dc550c0d956</t>
+          <t>https://www.indeed.com/viewjob?jk=37cd157df749b9e8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ryan Companies US, Inc.</t>
+          <t>ICAT Logistics, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea1d0eeb00ba384</t>
+          <t>https://www.indeed.com/viewjob?jk=490396287ca9423d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336bfe0af38918a1</t>
+          <t>https://www.indeed.com/viewjob?jk=eba11dc550c0d956</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SIGNITIVES</t>
+          <t>Ryan Companies US, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afef76c3c4cb302e</t>
+          <t>https://www.indeed.com/viewjob?jk=eea1d0eeb00ba384</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Anteriad</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Google Cloud Platform, Dataflow, Cloud Storage, Spark</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a53981dcd494255</t>
+          <t>https://www.indeed.com/viewjob?jk=336bfe0af38918a1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II (DevOps)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hi Marley</t>
+          <t>SIGNITIVES</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, DynamoDB, ETL, ELT</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e6ba06d3a7b30f</t>
+          <t>https://www.indeed.com/viewjob?jk=afef76c3c4cb302e</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Applied Information Sciences</t>
+          <t>Anteriad</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Google Cloud Platform, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4d756dafb24330</t>
+          <t>https://www.indeed.com/viewjob?jk=5a53981dcd494255</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Sr. Software Engineer II (DevOps)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lasting Change Inc</t>
+          <t>Hi Marley</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, Scala, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3a86d1b4b4bd7e7</t>
+          <t>https://www.indeed.com/viewjob?jk=57e6ba06d3a7b30f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Applied Information Sciences</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,104 +1256,104 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32f15966adb7c80c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4d756dafb24330</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lasting Change Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7433f9b8b5c4a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=b3a86d1b4b4bd7e7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Step Functions, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddf7449abdd32b05</t>
+          <t>https://www.indeed.com/viewjob?jk=32f15966adb7c80c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70728c10caf53950</t>
+          <t>https://www.indeed.com/viewjob?jk=5b155ae7711afa6e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Healthcare Data Platforms</t>
+          <t>Sr. Data Engineer - Cloud &amp; AI Platform [On-Site]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, GCP, BigQuery, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, EMR, RDS, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c87aef812edc38ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ba4a006c4d066d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Airvoyant</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TRAX USA Corp.</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,42 +1431,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1046b4cc869c21</t>
+          <t>https://www.indeed.com/viewjob?jk=426a2df1dcd32427</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Associate Data Engineer (REMOTE)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Snowflake, PostgreSQL, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5cff3964beedb24</t>
+          <t>https://www.indeed.com/viewjob?jk=f62c64972906caa0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, ML Platform | Parafin</t>
+          <t>Associate Data Engineer (REMOTE)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>carnaby fox</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4377663fa2ea1245</t>
+          <t>https://www.indeed.com/viewjob?jk=ad092c66101d7698</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer - III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Noise Consulting Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,137 +1546,137 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2baa480224d46766</t>
+          <t>https://www.indeed.com/viewjob?jk=7433f9b8b5c4a5a6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c980ae96d7c71b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=ddf7449abdd32b05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior BI Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Walker &amp; Dunlop</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashua, NH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=827ebbc8cea913b8</t>
+          <t>https://www.indeed.com/viewjob?jk=70728c10caf53950</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AWS Architect</t>
+          <t>Senior Data Engineer – Healthcare Data Platforms</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, GCP, BigQuery, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=723c6fbf1e8f4749</t>
+          <t>https://www.indeed.com/viewjob?jk=c87aef812edc38ba</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>AWS Public Cloud Senior Consultant</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Artisan Studios, LLC DBA Amy Howard At Home &amp; A Makers' Studio</t>
+          <t>Ensono</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Spark, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,59 +1686,59 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7350027af6d67644</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb217da2e922612</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Full Stack Developer - Airvoyant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>TRAX USA Corp.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34430b584944faaf</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1046b4cc869c21</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Integrations Architect- Azure</t>
+          <t>Data Engineer, Data Engineering and Analytics - USDS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Hadoop, HDFS, Hive, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a988b9cc3e868674</t>
+          <t>https://www.indeed.com/viewjob?jk=d72ef2291619fe5e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Data &amp; AI Infrastructure</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>McKinney</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, MongoDB, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Event Hubs, Snowflake, PostgreSQL, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad3b7a6b278561a</t>
+          <t>https://www.indeed.com/viewjob?jk=a5cff3964beedb24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Development Engineer â€“ Backend / Platform</t>
+          <t>Senior Software Engineer, ML Platform | Parafin</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>carnaby fox</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kinesis, IAM, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a635808e4af271</t>
+          <t>https://www.indeed.com/viewjob?jk=4377663fa2ea1245</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer (contract)</t>
+          <t>Data Engineer - III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Noise Consulting Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Spark, Scala, Kafka, Talend, CI/CD, Maven</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09530a3bb367b138</t>
+          <t>https://www.indeed.com/viewjob?jk=2baa480224d46766</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer - Remote</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea777f331fdeff3</t>
+          <t>https://www.indeed.com/viewjob?jk=c980ae96d7c71b5b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>AWS Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47eb49ae40d3103f</t>
+          <t>https://www.indeed.com/viewjob?jk=723c6fbf1e8f4749</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Artisan Studios, LLC DBA Amy Howard At Home &amp; A Makers' Studio</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, IAM, RDS, Spark, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837b89c39e0b1f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=7350027af6d67644</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101a2c6e0c8a3069</t>
+          <t>https://www.indeed.com/viewjob?jk=34430b584944faaf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Application Architect (contract)</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c4dc6b11200157</t>
+          <t>https://www.indeed.com/viewjob?jk=a988b9cc3e868674</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Contact Center Architect – Healthcare &amp; Amazon Connect – R01566032</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Verification Technologies LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Henderson, NV, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, Athena, Timestream, Step Functions, S3, SQS, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,137 +2071,137 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baab0523b145fc75</t>
+          <t>https://www.indeed.com/viewjob?jk=97a02535a97e1c4c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric, Power BI)</t>
+          <t>Senior Platform Engineer, Data &amp; AI Infrastructure</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>McKinney</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Kimball, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, MongoDB, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0500d4e766982809</t>
+          <t>https://www.indeed.com/viewjob?jk=fad3b7a6b278561a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior BI Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Walker &amp; Dunlop</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, SQS, API Gateway, ECS, RDS, Jenkins</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e888182752c6207b</t>
+          <t>https://www.indeed.com/viewjob?jk=827ebbc8cea913b8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer â€“ Backend / Platform</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ceresti Health</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PostgreSQL, Data Modeling, Kimball, dbt, CI/CD, Airflow</t>
+          <t>Kinesis, IAM, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94bd4f4546ea6e61</t>
+          <t>https://www.indeed.com/viewjob?jk=41a635808e4af271</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Informatica ETL Developer - 6326296</t>
+          <t>Data Analytical Engineer, Payment Data Intelligence - USDS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1a17c04578e9be3</t>
+          <t>https://www.indeed.com/viewjob?jk=a567c2b339c20c2f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Informatica ETL Developer - 6326296</t>
+          <t>Azure Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21eab84e17f0b1ac</t>
+          <t>https://www.indeed.com/viewjob?jk=809ad06a2b50c327</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Informatica ETL Developer - 6326296</t>
+          <t>Cloud Data Platform Engineer - Remote</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40516db2dcf106b5</t>
+          <t>https://www.indeed.com/viewjob?jk=dea777f331fdeff3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AWS Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564f104de61b3f0a</t>
+          <t>https://www.indeed.com/viewjob?jk=45e8be79fa6bbbf1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1849a5b7a2f2af9b</t>
+          <t>https://www.indeed.com/viewjob?jk=47eb49ae40d3103f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Safelease</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6884b300f1b32ae4</t>
+          <t>https://www.indeed.com/viewjob?jk=837b89c39e0b1f1d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Power BI, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=213170f837efaaa7</t>
+          <t>https://www.indeed.com/viewjob?jk=101a2c6e0c8a3069</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full Stack Cloud Engineer</t>
+          <t>Application Architect (contract)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Akanksha LLC</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf16acc114cd913</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c4dc6b11200157</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>Contact Center Architect – Healthcare &amp; Amazon Connect – R01566032</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a083efe79b22465</t>
+          <t>https://www.indeed.com/viewjob?jk=baab0523b145fc75</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>DPL Trading Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Montclair, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233d27bbc07fd70f</t>
+          <t>https://www.indeed.com/viewjob?jk=55a4531f3c73b952</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full Stack Senior Engineer, Application Development</t>
+          <t>Software Engineer, Data Privacy &amp; Infrastructure - USDS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, HDFS, Hive, Spark, Kafka, MySQL, NoSQL, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c25c1b0bc5a8d73</t>
+          <t>https://www.indeed.com/viewjob?jk=625f5552fcee590f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, SQS, API Gateway, ECS, RDS, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e209bbb5ba8b89</t>
+          <t>https://www.indeed.com/viewjob?jk=e888182752c6207b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Ceresti Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, S3, RDS, Spark, PostgreSQL, Data Modeling, Kimball, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1aed5a774867a44</t>
+          <t>https://www.indeed.com/viewjob?jk=94bd4f4546ea6e61</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Vytl Controls Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69b02ec8d04b37bb</t>
+          <t>https://www.indeed.com/viewjob?jk=2f97f2d7c736b559</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AWS Developer / Administrator</t>
+          <t>Informatica ETL Developer - 6326296</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,54 +2701,54 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3c84e2687fbb09</t>
+          <t>https://www.indeed.com/viewjob?jk=e1a17c04578e9be3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>Informatica ETL Developer - 6326296</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=538c5daa04e61b19</t>
+          <t>https://www.indeed.com/viewjob?jk=21eab84e17f0b1ac</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Informatica ETL Developer - 6326296</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2757,81 +2757,81 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb44a4b768419ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=40516db2dcf106b5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Oracle)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, dbt, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b698f84637b7e148</t>
+          <t>https://www.indeed.com/viewjob?jk=564f104de61b3f0a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d604ebca572d9a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=1849a5b7a2f2af9b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Safelease</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244f96a693bca9f8</t>
+          <t>https://www.indeed.com/viewjob?jk=6884b300f1b32ae4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Power BI, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4229f7f9f0a4e0f7</t>
+          <t>https://www.indeed.com/viewjob?jk=213170f837efaaa7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Technical Scrum Master</t>
+          <t>Full Stack Cloud Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>The Akanksha LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, API Gateway, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3405192fd1717731</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf16acc114cd913</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Natera</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d57e3def97a538</t>
+          <t>https://www.indeed.com/viewjob?jk=0a083efe79b22465</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist- Financial Services</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d86224c98360290</t>
+          <t>https://www.indeed.com/viewjob?jk=233d27bbc07fd70f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Full Stack Senior Engineer, Application Development</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Spark, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Blob Storage, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a874d216618930</t>
+          <t>https://www.indeed.com/viewjob?jk=3c25c1b0bc5a8d73</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Data Modeling, MLOps, Git, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,137 +3086,137 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5518f07c3a7fbfc2</t>
+          <t>https://www.indeed.com/viewjob?jk=69b02ec8d04b37bb</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Sr. Info Security Engineer (Netskope ZTNA platform)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kirkland &amp; Ellis</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0219ec8577fe8e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8fd7f561e18c20</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr AI Platform Engineer</t>
+          <t>Sr. Info Security Engineer (Netskope ZTNA platform)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f8d87a308d60fa</t>
+          <t>https://www.indeed.com/viewjob?jk=f368e82295b031ae</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist, Healthcare &amp; Life Sciences</t>
+          <t>Sr. Info Security Engineer (Netskope ZTNA platform)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa967f56c6eb5ef3</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf2be9c62be8976</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Center for Diagnostics and Artificial Intelligence</t>
+          <t>Sr. Info Security Engineer (Netskope ZTNA platform)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cleveland Clinic</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,94 +3226,94 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10aaff122c10f274</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7c8b6554940fe0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Info Security Engineer (Netskope ZTNA platform)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sidley Austin</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0414967af8c69f06</t>
+          <t>https://www.indeed.com/viewjob?jk=de008b9b9a2a19be</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>AWS Developer / Administrator</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, SQL Server, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e1b874414bff22</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3c84e2687fbb09</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI Full Stack Engineer</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Roche</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,612 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb44a4b768419ca2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Oracle)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Bitscopic</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b698f84637b7e148</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Technical Scrum Master</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3405192fd1717731</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist- Financial Services</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d86224c98360290</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Sigma Computing</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Redshift, Databricks, BigQuery, Spark, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90a874d216618930</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Kirkland &amp; Ellis</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a65f6db57ee3cc</t>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5518f07c3a7fbfc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Kirkland &amp; Ellis</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0219ec8577fe8e4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Sr AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Appex Innovation</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Unity Catalog, Kafka, Time Travel, Data Modeling, ELT, Power BI, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5f8d87a308d60fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist, Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Central, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa967f56c6eb5ef3</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, PySpark, Scala, Kafka, ELT, pytest, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd69f161aa8e715c</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d604ebca572d9a0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=244f96a693bca9f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, MongoDB, NoSQL, Splunk, CI/CD, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4229f7f9f0a4e0f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Natera</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, Scala, MLOps, MLflow, CI/CD, Terraform, Kubernetes, Datadog</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14d57e3def97a538</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Software Engineer - Java &amp; OpenText Extreme</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd6ce5169df5e00d</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AI Software Engineer - Center for Diagnostics and Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Cleveland Clinic</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=10aaff122c10f274</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Data Engineer - Java - Loops</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Copperleaf Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, CI/CD, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe4ff78e6fcedc19</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Data Consultant – Data Engineer &amp; Governance</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Quisitive</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cd77d29cb01573c</t>
         </is>
       </c>
     </row>
